--- a/salon_forms/008_skincare_questionnaire--salon_forms.xlsx
+++ b/salon_forms/008_skincare_questionnaire--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'oily'}</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Oily'}</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'sensitive'}</t>
+          <t>sensitive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Sensitive'}</t>
+          <t>Sensitive</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'dry'}</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Dry'}</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'combination'}</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Combination'}</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'skincare'}</t>
+          <t>skincare</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Skincare'}</t>
+          <t>Skincare</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'haircare'}</t>
+          <t>haircare</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Haircare'}</t>
+          <t>Haircare</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'cosmetics'}</t>
+          <t>cosmetics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Cosmetics'}</t>
+          <t>Cosmetics</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'fragrance'}</t>
+          <t>fragrance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Fragrance'}</t>
+          <t>Fragrance</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'acne'}</t>
+          <t>acne</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Acne'}</t>
+          <t>Acne</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'aging'}</t>
+          <t>aging</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Aging'}</t>
+          <t>Aging</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'hyper-pigmentation'}</t>
+          <t>hyper-pigmentation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Hyper-pigmentation'}</t>
+          <t>Hyper-pigmentation</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'sensitive_skin'}</t>
+          <t>sensitive_skin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Sensitive skin'}</t>
+          <t>Sensitive skin</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'rosacea'}</t>
+          <t>rosacea</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Rosacea'}</t>
+          <t>Rosacea</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'dark'}</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Dark'}</t>
+          <t>Dark</t>
         </is>
       </c>
     </row>
